--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_203_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_203_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.701</v>
+        <v>5.7432</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2956</v>
+        <v>4.2706</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4054</v>
+        <v>1.4726</v>
       </c>
       <c r="G2" t="n">
         <v>3.1359</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4349</v>
+        <v>0.6073</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3576</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0101</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4036</v>
+        <v>3.4879</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5584</v>
+        <v>3.6763</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1548</v>
+        <v>-0.1884</v>
       </c>
       <c r="G3" t="n">
         <v>1.0631</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3431</v>
+        <v>0.4274</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6418</v>
+        <v>0.6082</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7873</v>
+        <v>0.8615</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2312</v>
+        <v>0.6415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5561</v>
+        <v>0.22</v>
       </c>
       <c r="G4" t="n">
         <v>0.5295</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6316</v>
+        <v>0.7057</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0499</v>
+        <v>0.4602</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5816</v>
+        <v>0.2456</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0596</v>
+        <v>0.0745</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8004</v>
+        <v>0.9498</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7408</v>
+        <v>-0.8753</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5389</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0597</v>
+        <v>0.0747</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1019</v>
+        <v>0.0474</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1617</v>
+        <v>0.0272</v>
       </c>
       <c r="V5" t="n">
         <v>1.4665</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1386</v>
+        <v>-0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3851</v>
+        <v>1.0475</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-1.0505</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6021</v>
+        <v>-1.2686</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5485</v>
+        <v>-1.2987</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0535</v>
+        <v>0.0301</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3025</v>
+        <v>1.4375</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3025</v>
+        <v>0.4572</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9045</v>
+        <v>-2.7061</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.851</v>
+        <v>-1.756</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0535</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2315</v>
+        <v>0.7991</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.8573</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1489</v>
+        <v>-0.0582</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6742</v>
+        <v>-0.0035</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5443</v>
+        <v>0.621</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2185</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2686</v>
+        <v>-0.6021</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2987</v>
+        <v>-0.5485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0301</v>
+        <v>-0.0535</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4375</v>
+        <v>0.3025</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4572</v>
+        <v>0.3025</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9802999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7061</v>
+        <v>-0.9045</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.756</v>
+        <v>-0.851</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.0535</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1278</v>
+        <v>0.3666</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3541</v>
+        <v>0.3185</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2262</v>
+        <v>0.0481</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9029</v>
+        <v>-0.92</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3108</v>
+        <v>0.1928</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2137</v>
+        <v>-1.1129</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1615</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5627</v>
+        <v>0.5456</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6528</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.692</v>
+        <v>-1.4486</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5186</v>
+        <v>0.6253</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1734</v>
+        <v>-2.0738</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.021</v>
+        <v>0.6486</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7959</v>
+        <v>1.6757</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2251</v>
+        <v>-1.0271</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5767</v>
+        <v>2.1033</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8802</v>
+        <v>1.9193</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6965</v>
+        <v>0.184</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4443</v>
+        <v>-1.4547</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9157</v>
+        <v>-0.2435</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5286</v>
+        <v>-1.2112</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4914</v>
+        <v>-0.1847</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0761</v>
+        <v>-0.3183</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5847</v>
+        <v>0.1336</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0713</v>
+        <v>-2.4197</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2714</v>
+        <v>-2.5487</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3427</v>
+        <v>0.1291</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6486</v>
+        <v>-4.021</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6757</v>
+        <v>-1.7959</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0271</v>
+        <v>-2.2251</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1033</v>
+        <v>-2.5767</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9193</v>
+        <v>-0.8802</v>
       </c>
       <c r="L10" t="n">
-        <v>0.184</v>
+        <v>-1.6965</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4547</v>
+        <v>-1.4443</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2435</v>
+        <v>-0.9157</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2112</v>
+        <v>-0.5286</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8074</v>
+        <v>0.7637</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>1.046</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1353</v>
+        <v>-0.2822</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9814</v>
+        <v>-2.9363</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0978</v>
+        <v>-2.3805</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0196</v>
+        <v>-2.8239</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6051</v>
+        <v>0.3012</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5855</v>
+        <v>-3.1252</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2542</v>
+        <v>-0.5078</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7002</v>
+        <v>0.8808</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9543</v>
+        <v>-1.3887</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2738</v>
+        <v>-2.3161</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9049</v>
+        <v>-0.5796</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3688</v>
+        <v>-1.7365</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.2473</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2133</v>
+        <v>0.4237</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7512</v>
+        <v>0.0395</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4621</v>
+        <v>0.3842</v>
       </c>
       <c r="V11" t="n">
+        <v>-0.5361</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.0722</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.7501</v>
-      </c>
       <c r="X11" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0372</v>
+        <v>-3.5204</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.3554</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4813</v>
+        <v>-2.165</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8239</v>
+        <v>-2.0196</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3012</v>
+        <v>-2.6051</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1252</v>
+        <v>0.5855</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5078</v>
+        <v>1.2542</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8808</v>
+        <v>-1.7002</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3887</v>
+        <v>2.9543</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3161</v>
+        <v>-3.2738</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5796</v>
+        <v>-0.9049</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7365</v>
+        <v>-2.3688</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3229</v>
+        <v>0.6743</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0395</v>
+        <v>0.2794</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2834</v>
+        <v>0.3949</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0722</v>
+        <v>1.7501</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5265</v>
+        <v>-5.2414</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0882</v>
+        <v>-3.4671</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4382</v>
+        <v>-1.7743</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9666</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0237</v>
+        <v>0.2614</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4481</v>
+        <v>0.1731</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4244</v>
+        <v>0.0883</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.072600000000001</v>
+        <v>-6.325800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3509</v>
+        <v>4.0977</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.4234</v>
+        <v>-10.4235</v>
       </c>
       <c r="G14" t="n">
         <v>-11.0251</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5728</v>
+        <v>-1.572800000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-9.452399999999999</v>
@@ -1546,13 +1546,13 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>4.718</v>
+        <v>5.464799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1278</v>
+        <v>3.8745</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5903</v>
+        <v>1.5904</v>
       </c>
       <c r="V14" t="n">
         <v>0.3943000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5325</v>
+        <v>6.6061</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8897</v>
+        <v>6.0077</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6428</v>
+        <v>0.5985</v>
       </c>
       <c r="G15" t="n">
         <v>5.598</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3154</v>
+        <v>-0.2418</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U15" t="n">
-        <v>0.058</v>
+        <v>0.0136</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2481</v>
+        <v>3.524</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8015</v>
+        <v>4.1554</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5534</v>
+        <v>-0.6314</v>
       </c>
       <c r="G16" t="n">
         <v>1.2717</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1138</v>
+        <v>0.1621</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U16" t="n">
-        <v>0.409</v>
+        <v>0.331</v>
       </c>
       <c r="V16" t="n">
         <v>0.9304</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6486</v>
+        <v>1.5508</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7565</v>
+        <v>0.5313</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1079</v>
+        <v>1.0195</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6785</v>
+        <v>1.6433</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7588</v>
+        <v>2.0347</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0803</v>
+        <v>-0.3914</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3436</v>
+        <v>2.4693</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1595</v>
+        <v>2.9612</v>
       </c>
       <c r="L17" t="n">
-        <v>0.184</v>
+        <v>-0.4919</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6651</v>
+        <v>-0.826</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4008</v>
+        <v>-0.9265</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2643</v>
+        <v>0.1005</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4187</v>
+        <v>-1.0203</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4129</v>
+        <v>-0.7782</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0057</v>
+        <v>-0.242</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4772</v>
+        <v>1.166</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4133</v>
+        <v>1.2847</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0639</v>
+        <v>-0.1187</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6433</v>
+        <v>0.6785</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0347</v>
+        <v>0.7588</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3914</v>
+        <v>-0.0803</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4693</v>
+        <v>1.3436</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9612</v>
+        <v>1.1595</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4919</v>
+        <v>0.184</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.826</v>
+        <v>-0.6651</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9265</v>
+        <v>-0.4008</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1005</v>
+        <v>-0.2643</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0939</v>
+        <v>-0.0639</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8962</v>
+        <v>-0.0589</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1977</v>
+        <v>-0.005</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1001</v>
+        <v>0.9816</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3549</v>
+        <v>-0.5027</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2547</v>
+        <v>1.4844</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8383</v>
+        <v>-0.4398</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9385</v>
+        <v>-0.0048</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1002</v>
+        <v>-0.435</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4327</v>
+        <v>-0.3966</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2119</v>
+        <v>0.3529</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2208</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5944</v>
+        <v>-0.0431</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2734</v>
+        <v>-0.3577</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3211</v>
+        <v>0.3145</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8159</v>
+        <v>-0.3646</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2596</v>
+        <v>-0.1061</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4437</v>
+        <v>-0.2585</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9304</v>
+        <v>0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6728</v>
+        <v>0.8299</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6207</v>
+        <v>3.0625</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2935</v>
+        <v>-2.2326</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4398</v>
+        <v>2.6135</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0048</v>
+        <v>0.9772</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.435</v>
+        <v>1.6363</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3966</v>
+        <v>3.9149</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3529</v>
+        <v>2.2722</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.6428</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0431</v>
+        <v>-1.3015</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3577</v>
+        <v>-1.2949</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3145</v>
+        <v>-0.0065</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6734</v>
+        <v>-0.6418</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.224</v>
+        <v>-0.1412</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4494</v>
+        <v>-0.5006</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3943</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3943</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3194</v>
+        <v>-0.4158</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9445</v>
+        <v>1.3365</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6251</v>
+        <v>-1.7523</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6135</v>
+        <v>1.6029</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9772</v>
+        <v>-1.3349</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6363</v>
+        <v>2.9377</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9149</v>
+        <v>3.5657</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2722</v>
+        <v>0.4642</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6428</v>
+        <v>3.1015</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3015</v>
+        <v>-1.9629</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2949</v>
+        <v>-1.7991</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0065</v>
+        <v>-0.1638</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1523</v>
+        <v>-0.6811</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2592</v>
+        <v>-0.4125</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8931</v>
+        <v>-0.2686</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6083</v>
+        <v>2.8223</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2862</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3815</v>
+        <v>-0.782</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6288</v>
+        <v>0.1138</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0103</v>
+        <v>-0.8958</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6029</v>
+        <v>0.8383</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3349</v>
+        <v>0.9385</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9377</v>
+        <v>-0.1002</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5657</v>
+        <v>2.4327</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4642</v>
+        <v>2.2119</v>
       </c>
       <c r="L22" t="n">
-        <v>3.1015</v>
+        <v>0.2208</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9629</v>
+        <v>-1.5944</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7991</v>
+        <v>-1.2734</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1638</v>
+        <v>-0.3211</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5515</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.639</v>
+        <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6469</v>
+        <v>0.9337</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1202</v>
+        <v>1.0185</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.0848</v>
       </c>
       <c r="V22" t="n">
-        <v>1.214</v>
+        <v>-0.9304</v>
       </c>
       <c r="W22" t="n">
-        <v>2.8223</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4123</v>
+        <v>-0.7833</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3837</v>
+        <v>-1.9119</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9714</v>
+        <v>1.1287</v>
       </c>
       <c r="G23" t="n">
         <v>0.1679</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4901</v>
+        <v>-0.861</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5939</v>
+        <v>-0.4367</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1324</v>
+        <v>-4.0321</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3615</v>
+        <v>-3.6538</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7709</v>
+        <v>-0.3784</v>
       </c>
       <c r="G24" t="n">
         <v>-2.9491</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4668</v>
+        <v>-0.3666</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9709</v>
+        <v>-0.2631</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.496</v>
+        <v>-0.1034</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2525</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.072500000000001</v>
+        <v>8.645199999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>10.4233</v>
+        <v>10.4235</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.350700000000001</v>
+        <v>-1.7781</v>
       </c>
       <c r="G25" t="n">
         <v>11.0252</v>
@@ -2404,13 +2404,13 @@
         <v>17.3965</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.718</v>
+        <v>-3.1453</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5904</v>
+        <v>-1.5903</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.1278</v>
+        <v>-1.555</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3943000000000001</v>
